--- a/StructureDefinition-Person-Person.xlsx
+++ b/StructureDefinition-Person-Person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Person-Person.xlsx
+++ b/StructureDefinition-Person-Person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,6 +273,10 @@
     <t>Source attribute: namn</t>
   </si>
   <si>
+    <t>Angivelse av personnamn sammanslaget enligt formatet "Mellannamn Efternamn, Förnamn".
+Om flera namn av samma typ förekommer ska dessa separeras med mellanslag.</t>
+  </si>
+  <si>
     <t>Person-Person.fodelsetidpunkt</t>
   </si>
   <si>
@@ -283,6 +287,11 @@
     <t>Source attribute: födelsetidpunkt</t>
   </si>
   <si>
+    <t>Angivelse av datum och eventuell tidpunkt då patienten är född.
+Ska användas om patienten inte har personnummer samt i vissa fall för spädbarn. Om fullständigt födelsedatum inte är känt, anges uppskattad födelsetid. Exakt klockslag kan vara intressant för nyfödda barn, men formatet tillåter lägre precision:
+Format: SSÅÅMMDDThhmmss, SSÅÅMMDDThhmm, SSÅÅMMDD, SSÅÅMM</t>
+  </si>
+  <si>
     <t>Person-Person.kon</t>
   </si>
   <si>
@@ -291,6 +300,9 @@
   </si>
   <si>
     <t>Source attribute: kön</t>
+  </si>
+  <si>
+    <t>Kod för patientens kön enligt folkbokföringen.</t>
   </si>
   <si>
     <t>Person-Person.antarRollen</t>
@@ -986,7 +998,7 @@
         <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1054,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1080,13 +1092,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1137,7 +1149,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1154,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1180,13 +1192,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1237,7 +1249,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1254,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1280,13 +1292,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1337,7 +1349,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
